--- a/hira_material_automation/output/monthly/202601_202608__nonmetal_anchor__040019__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202608__nonmetal_anchor__040019__normalized.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-04T22:16:40</t>
+          <t>2026-08-14T21:28:38</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8c85ec5a9ead656095d28b4de952cf1fc57d08f7d110b1da373b0bd3219e414b</t>
+          <t>8c8d1ee78ffc9de74bde79c09c533101245a6ea34e0b5bc4e76e1aaefff47043</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202608__nonmetal_anchor__040019__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202608__nonmetal_anchor__040019__normalized.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-14T21:28:38</t>
+          <t>2026-08-24T21:33:49</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8c8d1ee78ffc9de74bde79c09c533101245a6ea34e0b5bc4e76e1aaefff47043</t>
+          <t>07f0d5689bf2b7039671886d5278ff48ca57d21756afce962f6d472bcda27776</t>
         </is>
       </c>
     </row>
